--- a/GameData/DataTables/Meta/StageReleaseTable.xlsx
+++ b/GameData/DataTables/Meta/StageReleaseTable.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H43"/>
+  <dimension ref="A1:H58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1557,6 +1557,396 @@
         </is>
       </c>
     </row>
+    <row r="44">
+      <c r="B44" t="n">
+        <v>40</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>C-001</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>2</v>
+      </c>
+      <c r="F44" t="n">
+        <v>1</v>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>B1 资格后由节拍器委托或舞蹈教室求助引出</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>本批资格＋完成本案触发调查后创建怪谈；回访领奖不阻挡下一批</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" t="n">
+        <v>41</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>C-002</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>2</v>
+      </c>
+      <c r="F45" t="n">
+        <v>2</v>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>B2 资格后由裁缝铺照明委托或求助引出</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>本批资格＋完成本案触发调查后创建怪谈；回访领奖不阻挡下一批</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="B46" t="n">
+        <v>42</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>C-003</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>2</v>
+      </c>
+      <c r="F46" t="n">
+        <v>3</v>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>B3 资格后由保管匣维修或仓库求助引出</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>本批资格＋完成本案触发调查后创建怪谈；回访领奖不阻挡下一批</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" t="n">
+        <v>43</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>C-004</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>2</v>
+      </c>
+      <c r="F47" t="n">
+        <v>4</v>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>B4 资格后由旧图整理或收藏馆画面检查引出</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>本批资格＋完成本案触发调查后创建怪谈；回访领奖不阻挡下一批</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" t="n">
+        <v>44</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>C-005</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>2</v>
+      </c>
+      <c r="F48" t="n">
+        <v>3</v>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>B3 资格后由河岸旧院灯具委托或看守失联引出</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>本批资格＋完成本案触发调查后创建怪谈；回访领奖不阻挡下一批</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="B49" t="n">
+        <v>45</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>C-006</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>2</v>
+      </c>
+      <c r="F49" t="n">
+        <v>3</v>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>B3 资格后由仓库夹层门框检查或求救引出</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>本批资格＋完成本案触发调查后创建怪谈；回访领奖不阻挡下一批</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" t="n">
+        <v>46</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>C-007</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>2</v>
+      </c>
+      <c r="F50" t="n">
+        <v>3</v>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>B3 资格后由摄影工作室镜架维修或查看请求引出</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>本批资格＋完成本案触发调查后创建怪谈；回访领奖不阻挡下一批</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" t="n">
+        <v>47</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>C-008</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>2</v>
+      </c>
+      <c r="F51" t="n">
+        <v>4</v>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>B4 资格后由旅馆日间维修或住客唤醒请求引出</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>本批资格＋完成本案触发调查后创建怪谈；回访领奖不阻挡下一批</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="B52" t="n">
+        <v>48</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>C-009</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>2</v>
+      </c>
+      <c r="F52" t="n">
+        <v>2</v>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>B2 资格后由活动中心清洁设备检查或积水处置引出</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>本批资格＋完成本案触发调查后创建怪谈；回访领奖不阻挡下一批</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="B53" t="n">
+        <v>49</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>C-010</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>2</v>
+      </c>
+      <c r="F53" t="n">
+        <v>4</v>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>B4 资格后由收藏馆侧厅画框维修或负荷求助引出</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>本批资格＋完成本案触发调查后创建怪谈；回访领奖不阻挡下一批</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="B54" t="n">
+        <v>50</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>C-011</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>2</v>
+      </c>
+      <c r="F54" t="n">
+        <v>4</v>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>B4 资格后由商街活动设备维修或履约核对引出</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>本批资格＋完成本案触发调查后创建怪谈；回访领奖不阻挡下一批</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="n">
+        <v>51</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>C-012</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>2</v>
+      </c>
+      <c r="F55" t="n">
+        <v>4</v>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>B4 资格后由阅览室灯具维修或影子异常引出</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>本批资格＋完成本案触发调查后创建怪谈；回访领奖不阻挡下一批</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="B56" t="n">
+        <v>52</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>C-013</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>2</v>
+      </c>
+      <c r="F56" t="n">
+        <v>2</v>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>B2 资格后由补习班街区车灯维修或学生求助引出</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>本批资格＋完成本案触发调查后创建怪谈；回访领奖不阻挡下一批</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="B57" t="n">
+        <v>53</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>C-014</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>2</v>
+      </c>
+      <c r="F57" t="n">
+        <v>3</v>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>B3 资格后由旧校舍门锁线路维修或校舍求助引出</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>本批资格＋完成本案触发调查后创建怪谈；回访领奖不阻挡下一批</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="B58" t="n">
+        <v>54</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>C-015</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>2</v>
+      </c>
+      <c r="F58" t="n">
+        <v>5</v>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>B5 资格后由配送设备维护或末站失联报告引出</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>本批资格＋完成本案触发调查后创建怪谈；回访领奖不阻挡下一批</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
